--- a/2025/PC_trends_2016_2025_cleaned.xlsx
+++ b/2025/PC_trends_2016_2025_cleaned.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
   <si>
     <t xml:space="preserve">Site</t>
   </si>
@@ -44,9 +44,6 @@
     <t xml:space="preserve">Magnitude</t>
   </si>
   <si>
-    <t xml:space="preserve">p_value</t>
-  </si>
-  <si>
     <t xml:space="preserve">01-01</t>
   </si>
   <si>
@@ -176,15 +173,6 @@
     <t xml:space="preserve">1604B1</t>
   </si>
   <si>
-    <t xml:space="preserve">22-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LONG BRANCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1627</t>
-  </si>
-  <si>
     <t xml:space="preserve">24-02</t>
   </si>
   <si>
@@ -219,6 +207,15 @@
   </si>
   <si>
     <t xml:space="preserve">1633E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BONN CREEK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1668D</t>
   </si>
   <si>
     <t xml:space="preserve">E1</t>
@@ -713,19 +710,16 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>28.157197</v>
@@ -734,33 +728,30 @@
         <v>-82.757037</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
         <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.0629</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
       </c>
       <c r="D3" t="n">
         <v>28.086325</v>
@@ -769,33 +760,30 @@
         <v>-82.694148</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
         <v>7</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.0516</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
       </c>
       <c r="D4" t="n">
         <v>28.086325</v>
@@ -804,33 +792,30 @@
         <v>-82.694148</v>
       </c>
       <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I4" t="s">
         <v>22</v>
       </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" t="s">
-        <v>23</v>
-      </c>
       <c r="J4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.0715</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
       </c>
       <c r="D5" t="n">
         <v>28.068168</v>
@@ -839,33 +824,30 @@
         <v>-82.722861</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
         <v>7</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.0121</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
       </c>
       <c r="D6" t="n">
         <v>28.033754</v>
@@ -874,33 +856,30 @@
         <v>-82.780066</v>
       </c>
       <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" t="s">
         <v>30</v>
-      </c>
-      <c r="G6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.0398</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
         <v>32</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
       </c>
       <c r="D7" t="n">
         <v>27.979585</v>
@@ -909,33 +888,30 @@
         <v>-82.69525</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
         <v>7</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.0067</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
         <v>32</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>34</v>
       </c>
       <c r="D8" t="n">
         <v>27.979585</v>
@@ -944,33 +920,30 @@
         <v>-82.69525</v>
       </c>
       <c r="F8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" t="s">
         <v>35</v>
       </c>
-      <c r="G8" t="s">
-        <v>36</v>
-      </c>
       <c r="H8" t="s">
         <v>7</v>
       </c>
       <c r="I8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.0236</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
         <v>32</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>33</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
       </c>
       <c r="D9" t="n">
         <v>27.979585</v>
@@ -979,33 +952,30 @@
         <v>-82.69525</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
         <v>7</v>
       </c>
       <c r="I9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J9" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.0156</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
         <v>32</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
       </c>
       <c r="D10" t="n">
         <v>27.979585</v>
@@ -1014,33 +984,30 @@
         <v>-82.69525</v>
       </c>
       <c r="F10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" t="s">
         <v>22</v>
       </c>
-      <c r="G10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" t="s">
-        <v>23</v>
-      </c>
       <c r="J10" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.0031</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
         <v>38</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>39</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
       </c>
       <c r="D11" t="n">
         <v>27.974701</v>
@@ -1049,33 +1016,30 @@
         <v>-82.713548</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
         <v>7</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.0815</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" t="s">
         <v>41</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>42</v>
-      </c>
-      <c r="C12" t="s">
-        <v>43</v>
       </c>
       <c r="D12" t="n">
         <v>27.990174</v>
@@ -1084,33 +1048,30 @@
         <v>-82.783999</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
         <v>7</v>
       </c>
       <c r="I12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0.0691</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>42</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>27.990174</v>
@@ -1119,33 +1080,30 @@
         <v>-82.783999</v>
       </c>
       <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13" t="s">
         <v>22</v>
       </c>
-      <c r="G13" t="s">
-        <v>15</v>
-      </c>
-      <c r="H13" t="s">
-        <v>7</v>
-      </c>
-      <c r="I13" t="s">
-        <v>23</v>
-      </c>
       <c r="J13" t="s">
-        <v>17</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.05</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
         <v>41</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>42</v>
-      </c>
-      <c r="C14" t="s">
-        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>27.990174</v>
@@ -1154,33 +1112,30 @@
         <v>-82.783999</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
         <v>7</v>
       </c>
       <c r="I14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.0532</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" t="s">
         <v>44</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>45</v>
-      </c>
-      <c r="C15" t="s">
-        <v>46</v>
       </c>
       <c r="D15" t="n">
         <v>27.943531</v>
@@ -1189,33 +1144,30 @@
         <v>-82.805969</v>
       </c>
       <c r="F15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" t="s">
         <v>35</v>
       </c>
-      <c r="G15" t="s">
-        <v>36</v>
-      </c>
       <c r="H15" t="s">
         <v>7</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.0137</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
         <v>44</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>45</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>27.943531</v>
@@ -1224,33 +1176,30 @@
         <v>-82.805969</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" t="s">
         <v>7</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J16" t="s">
-        <v>17</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.0169</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
         <v>44</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>45</v>
-      </c>
-      <c r="C17" t="s">
-        <v>46</v>
       </c>
       <c r="D17" t="n">
         <v>27.943531</v>
@@ -1259,33 +1208,30 @@
         <v>-82.805969</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H17" t="s">
         <v>7</v>
       </c>
       <c r="I17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J17" t="s">
-        <v>17</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.0061</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
         <v>45</v>
-      </c>
-      <c r="C18" t="s">
-        <v>46</v>
       </c>
       <c r="D18" t="n">
         <v>27.940683</v>
@@ -1294,33 +1240,30 @@
         <v>-82.801349</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H18" t="s">
         <v>7</v>
       </c>
       <c r="I18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J18" t="s">
-        <v>17</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.0198</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" t="s">
         <v>48</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>49</v>
-      </c>
-      <c r="C19" t="s">
-        <v>50</v>
       </c>
       <c r="D19" t="n">
         <v>27.971475</v>
@@ -1329,33 +1272,30 @@
         <v>-82.78153</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H19" t="s">
         <v>7</v>
       </c>
       <c r="I19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J19" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.0492</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" t="s">
         <v>48</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>49</v>
-      </c>
-      <c r="C20" t="s">
-        <v>50</v>
       </c>
       <c r="D20" t="n">
         <v>27.971475</v>
@@ -1364,33 +1304,30 @@
         <v>-82.78153</v>
       </c>
       <c r="F20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" t="s">
         <v>35</v>
       </c>
-      <c r="G20" t="s">
-        <v>36</v>
-      </c>
       <c r="H20" t="s">
         <v>7</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J20" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.0527</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s">
         <v>48</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>49</v>
-      </c>
-      <c r="C21" t="s">
-        <v>50</v>
       </c>
       <c r="D21" t="n">
         <v>27.971475</v>
@@ -1399,33 +1336,30 @@
         <v>-82.78153</v>
       </c>
       <c r="F21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H21" t="s">
         <v>7</v>
       </c>
       <c r="I21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J21" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.0527</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" t="s">
         <v>48</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>49</v>
-      </c>
-      <c r="C22" t="s">
-        <v>50</v>
       </c>
       <c r="D22" t="n">
         <v>27.971475</v>
@@ -1434,33 +1368,30 @@
         <v>-82.78153</v>
       </c>
       <c r="F22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H22" t="s">
         <v>7</v>
       </c>
       <c r="I22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J22" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.0223</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" t="s">
         <v>48</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>49</v>
-      </c>
-      <c r="C23" t="s">
-        <v>50</v>
       </c>
       <c r="D23" t="n">
         <v>27.971475</v>
@@ -1469,33 +1400,30 @@
         <v>-82.78153</v>
       </c>
       <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I23" t="s">
         <v>22</v>
       </c>
-      <c r="G23" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" t="s">
-        <v>7</v>
-      </c>
-      <c r="I23" t="s">
-        <v>23</v>
-      </c>
       <c r="J23" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.0701</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>49</v>
-      </c>
-      <c r="C24" t="s">
-        <v>50</v>
       </c>
       <c r="D24" t="n">
         <v>27.971475</v>
@@ -1504,33 +1432,30 @@
         <v>-82.78153</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H24" t="s">
         <v>7</v>
       </c>
       <c r="I24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J24" t="s">
-        <v>17</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.0366</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" t="s">
         <v>51</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>52</v>
-      </c>
-      <c r="C25" t="s">
-        <v>53</v>
       </c>
       <c r="D25" t="n">
         <v>27.9407</v>
@@ -1539,33 +1464,30 @@
         <v>-82.759796</v>
       </c>
       <c r="F25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" t="s">
         <v>35</v>
       </c>
-      <c r="G25" t="s">
-        <v>36</v>
-      </c>
       <c r="H25" t="s">
         <v>7</v>
       </c>
       <c r="I25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J25" t="s">
-        <v>17</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.0106</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
         <v>51</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>52</v>
-      </c>
-      <c r="C26" t="s">
-        <v>53</v>
       </c>
       <c r="D26" t="n">
         <v>27.9407</v>
@@ -1574,33 +1496,30 @@
         <v>-82.759796</v>
       </c>
       <c r="F26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H26" t="s">
         <v>7</v>
       </c>
       <c r="I26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J26" t="s">
-        <v>17</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.0106</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" t="s">
         <v>51</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>52</v>
-      </c>
-      <c r="C27" t="s">
-        <v>53</v>
       </c>
       <c r="D27" t="n">
         <v>27.9407</v>
@@ -1609,138 +1528,126 @@
         <v>-82.759796</v>
       </c>
       <c r="F27" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" t="s">
+        <v>7</v>
+      </c>
+      <c r="I27" t="s">
         <v>22</v>
       </c>
-      <c r="G27" t="s">
-        <v>15</v>
-      </c>
-      <c r="H27" t="s">
-        <v>7</v>
-      </c>
-      <c r="I27" t="s">
-        <v>23</v>
-      </c>
       <c r="J27" t="s">
-        <v>17</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.0409</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" t="s">
         <v>54</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>55</v>
       </c>
-      <c r="C28" t="s">
-        <v>56</v>
-      </c>
       <c r="D28" t="n">
-        <v>27.91958</v>
+        <v>27.911902</v>
       </c>
       <c r="E28" t="n">
-        <v>-82.71975</v>
+        <v>-82.700352</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H28" t="s">
         <v>7</v>
       </c>
       <c r="I28" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J28" t="s">
-        <v>17</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.013</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" t="s">
         <v>57</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>58</v>
       </c>
-      <c r="C29" t="s">
-        <v>59</v>
-      </c>
       <c r="D29" t="n">
-        <v>27.911902</v>
+        <v>27.850126</v>
       </c>
       <c r="E29" t="n">
-        <v>-82.700352</v>
+        <v>-82.772943</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H29" t="s">
         <v>7</v>
       </c>
       <c r="I29" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J29" t="s">
-        <v>17</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.0052</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" t="s">
         <v>60</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>61</v>
       </c>
-      <c r="C30" t="s">
-        <v>62</v>
-      </c>
       <c r="D30" t="n">
-        <v>27.850126</v>
+        <v>27.891048</v>
       </c>
       <c r="E30" t="n">
-        <v>-82.772943</v>
+        <v>-82.824898</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H30" t="s">
         <v>7</v>
       </c>
       <c r="I30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J30" t="s">
-        <v>17</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.0019</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D31" t="n">
         <v>27.891048</v>
@@ -1749,68 +1656,62 @@
         <v>-82.824898</v>
       </c>
       <c r="F31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31" t="s">
         <v>22</v>
       </c>
-      <c r="G31" t="s">
-        <v>15</v>
-      </c>
-      <c r="H31" t="s">
-        <v>7</v>
-      </c>
-      <c r="I31" t="s">
-        <v>16</v>
-      </c>
       <c r="J31" t="s">
-        <v>17</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.0533</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" t="s">
         <v>63</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>64</v>
       </c>
-      <c r="C32" t="s">
-        <v>65</v>
-      </c>
       <c r="D32" t="n">
-        <v>27.891048</v>
+        <v>27.91212</v>
       </c>
       <c r="E32" t="n">
-        <v>-82.824898</v>
+        <v>-82.81387</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H32" t="s">
         <v>7</v>
       </c>
       <c r="I32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J32" t="s">
-        <v>17</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.0028</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C33" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D33" t="n">
         <v>27.91212</v>
@@ -1819,68 +1720,62 @@
         <v>-82.81387</v>
       </c>
       <c r="F33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G33" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="H33" t="s">
         <v>7</v>
       </c>
       <c r="I33" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J33" t="s">
-        <v>17</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.0108</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" t="s">
         <v>66</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>67</v>
       </c>
-      <c r="C34" t="s">
-        <v>68</v>
-      </c>
       <c r="D34" t="n">
-        <v>27.91212</v>
+        <v>27.822</v>
       </c>
       <c r="E34" t="n">
-        <v>-82.81387</v>
+        <v>-82.736</v>
       </c>
       <c r="F34" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H34" t="s">
         <v>7</v>
       </c>
       <c r="I34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J34" t="s">
-        <v>17</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.0108</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" t="s">
         <v>69</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>70</v>
-      </c>
-      <c r="C35" t="s">
-        <v>71</v>
       </c>
       <c r="D35" t="n">
         <v>27.982044</v>
@@ -1889,33 +1784,30 @@
         <v>-82.663591</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H35" t="s">
         <v>7</v>
       </c>
       <c r="I35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J35" t="s">
-        <v>17</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.0054</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" t="s">
         <v>72</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>73</v>
-      </c>
-      <c r="C36" t="s">
-        <v>74</v>
       </c>
       <c r="D36" t="n">
         <v>27.944683</v>
@@ -1924,33 +1816,30 @@
         <v>-82.711832</v>
       </c>
       <c r="F36" t="s">
+        <v>34</v>
+      </c>
+      <c r="G36" t="s">
         <v>35</v>
       </c>
-      <c r="G36" t="s">
-        <v>36</v>
-      </c>
       <c r="H36" t="s">
         <v>7</v>
       </c>
       <c r="I36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J36" t="s">
-        <v>17</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.0525</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" t="s">
         <v>72</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>73</v>
-      </c>
-      <c r="C37" t="s">
-        <v>74</v>
       </c>
       <c r="D37" t="n">
         <v>27.944683</v>
@@ -1959,33 +1848,30 @@
         <v>-82.711832</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H37" t="s">
         <v>7</v>
       </c>
       <c r="I37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J37" t="s">
-        <v>17</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.0127</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" t="s">
         <v>75</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>76</v>
-      </c>
-      <c r="C38" t="s">
-        <v>77</v>
       </c>
       <c r="D38" t="n">
         <v>27.937264</v>
@@ -1994,33 +1880,30 @@
         <v>-82.645195</v>
       </c>
       <c r="F38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H38" t="s">
         <v>7</v>
       </c>
       <c r="I38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J38" t="s">
-        <v>17</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.0199</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
         <v>75</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>76</v>
-      </c>
-      <c r="C39" t="s">
-        <v>77</v>
       </c>
       <c r="D39" t="n">
         <v>27.937264</v>
@@ -2029,33 +1912,30 @@
         <v>-82.645195</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H39" t="s">
         <v>7</v>
       </c>
       <c r="I39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J39" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.0038</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" t="s">
         <v>78</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>79</v>
-      </c>
-      <c r="C40" t="s">
-        <v>80</v>
       </c>
       <c r="D40" t="n">
         <v>27.895923</v>
@@ -2064,33 +1944,30 @@
         <v>-82.604644</v>
       </c>
       <c r="F40" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H40" t="s">
         <v>7</v>
       </c>
       <c r="I40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J40" t="s">
-        <v>17</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.0377</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>77</v>
+      </c>
+      <c r="B41" t="s">
         <v>78</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>79</v>
-      </c>
-      <c r="C41" t="s">
-        <v>80</v>
       </c>
       <c r="D41" t="n">
         <v>27.895923</v>
@@ -2099,33 +1976,30 @@
         <v>-82.604644</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H41" t="s">
         <v>7</v>
       </c>
       <c r="I41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J41" t="s">
-        <v>17</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.0059</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" t="s">
         <v>81</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>82</v>
-      </c>
-      <c r="C42" t="s">
-        <v>83</v>
       </c>
       <c r="D42" t="n">
         <v>27.854661</v>
@@ -2134,33 +2008,30 @@
         <v>-82.58336</v>
       </c>
       <c r="F42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H42" t="s">
         <v>7</v>
       </c>
       <c r="I42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J42" t="s">
-        <v>17</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0.0072</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>80</v>
+      </c>
+      <c r="B43" t="s">
         <v>81</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>82</v>
-      </c>
-      <c r="C43" t="s">
-        <v>83</v>
       </c>
       <c r="D43" t="n">
         <v>27.854661</v>
@@ -2169,33 +2040,30 @@
         <v>-82.58336</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H43" t="s">
         <v>7</v>
       </c>
       <c r="I43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J43" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.002</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44" t="s">
         <v>84</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>85</v>
-      </c>
-      <c r="C44" t="s">
-        <v>86</v>
       </c>
       <c r="D44" t="n">
         <v>28.117508</v>
@@ -2204,33 +2072,30 @@
         <v>-82.728277</v>
       </c>
       <c r="F44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H44" t="s">
         <v>7</v>
       </c>
       <c r="I44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J44" t="s">
-        <v>17</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.0453</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>83</v>
+      </c>
+      <c r="B45" t="s">
         <v>84</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>85</v>
-      </c>
-      <c r="C45" t="s">
-        <v>86</v>
       </c>
       <c r="D45" t="n">
         <v>28.117508</v>
@@ -2239,33 +2104,30 @@
         <v>-82.728277</v>
       </c>
       <c r="F45" t="s">
+        <v>21</v>
+      </c>
+      <c r="G45" t="s">
+        <v>14</v>
+      </c>
+      <c r="H45" t="s">
+        <v>7</v>
+      </c>
+      <c r="I45" t="s">
         <v>22</v>
       </c>
-      <c r="G45" t="s">
-        <v>15</v>
-      </c>
-      <c r="H45" t="s">
-        <v>7</v>
-      </c>
-      <c r="I45" t="s">
-        <v>23</v>
-      </c>
       <c r="J45" t="s">
-        <v>17</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.0219</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>83</v>
+      </c>
+      <c r="B46" t="s">
         <v>84</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>85</v>
-      </c>
-      <c r="C46" t="s">
-        <v>86</v>
       </c>
       <c r="D46" t="n">
         <v>28.117508</v>
@@ -2274,33 +2136,30 @@
         <v>-82.728277</v>
       </c>
       <c r="F46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H46" t="s">
         <v>7</v>
       </c>
       <c r="I46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J46" t="s">
-        <v>17</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.0535</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>86</v>
+      </c>
+      <c r="B47" t="s">
         <v>87</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>88</v>
-      </c>
-      <c r="C47" t="s">
-        <v>89</v>
       </c>
       <c r="D47" t="n">
         <v>27.851203</v>
@@ -2309,33 +2168,30 @@
         <v>-82.616182</v>
       </c>
       <c r="F47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H47" t="s">
         <v>7</v>
       </c>
       <c r="I47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J47" t="s">
-        <v>17</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0.05</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>86</v>
+      </c>
+      <c r="B48" t="s">
         <v>87</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>88</v>
-      </c>
-      <c r="C48" t="s">
-        <v>89</v>
       </c>
       <c r="D48" t="n">
         <v>27.851203</v>
@@ -2344,33 +2200,30 @@
         <v>-82.616182</v>
       </c>
       <c r="F48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H48" t="s">
         <v>7</v>
       </c>
       <c r="I48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J48" t="s">
-        <v>17</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.0084</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>89</v>
+      </c>
+      <c r="B49" t="s">
         <v>90</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>91</v>
-      </c>
-      <c r="C49" t="s">
-        <v>92</v>
       </c>
       <c r="D49" t="n">
         <v>27.878414</v>
@@ -2379,33 +2232,30 @@
         <v>-82.775218</v>
       </c>
       <c r="F49" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H49" t="s">
         <v>7</v>
       </c>
       <c r="I49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J49" t="s">
-        <v>17</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.0029</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>89</v>
+      </c>
+      <c r="B50" t="s">
         <v>90</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>91</v>
-      </c>
-      <c r="C50" t="s">
-        <v>92</v>
       </c>
       <c r="D50" t="n">
         <v>27.878414</v>
@@ -2414,33 +2264,30 @@
         <v>-82.775218</v>
       </c>
       <c r="F50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H50" t="s">
         <v>7</v>
       </c>
       <c r="I50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0.0128</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>89</v>
+      </c>
+      <c r="B51" t="s">
         <v>90</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>91</v>
-      </c>
-      <c r="C51" t="s">
-        <v>92</v>
       </c>
       <c r="D51" t="n">
         <v>27.878414</v>
@@ -2449,33 +2296,30 @@
         <v>-82.775218</v>
       </c>
       <c r="F51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H51" t="s">
         <v>7</v>
       </c>
       <c r="I51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J51" t="s">
-        <v>17</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0.0127</v>
+        <v>16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B52" t="s">
         <v>93</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>94</v>
-      </c>
-      <c r="C52" t="s">
-        <v>95</v>
       </c>
       <c r="D52" t="n">
         <v>28.115382</v>
@@ -2484,33 +2328,30 @@
         <v>-82.805717</v>
       </c>
       <c r="F52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H52" t="s">
         <v>7</v>
       </c>
       <c r="I52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J52" t="s">
-        <v>17</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0.0099</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>95</v>
+      </c>
+      <c r="B53" t="s">
         <v>96</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>97</v>
-      </c>
-      <c r="C53" t="s">
-        <v>98</v>
       </c>
       <c r="D53" t="n">
         <v>28.019274</v>
@@ -2519,33 +2360,30 @@
         <v>-82.805357</v>
       </c>
       <c r="F53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H53" t="s">
         <v>7</v>
       </c>
       <c r="I53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J53" t="s">
-        <v>17</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0.0119</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>98</v>
+      </c>
+      <c r="B54" t="s">
         <v>99</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>100</v>
-      </c>
-      <c r="C54" t="s">
-        <v>101</v>
       </c>
       <c r="D54" t="n">
         <v>27.941201</v>
@@ -2554,33 +2392,30 @@
         <v>-82.82485</v>
       </c>
       <c r="F54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H54" t="s">
         <v>7</v>
       </c>
       <c r="I54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J54" t="s">
-        <v>17</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0.0342</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>98</v>
+      </c>
+      <c r="B55" t="s">
         <v>99</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>100</v>
-      </c>
-      <c r="C55" t="s">
-        <v>101</v>
       </c>
       <c r="D55" t="n">
         <v>27.941201</v>
@@ -2589,33 +2424,30 @@
         <v>-82.82485</v>
       </c>
       <c r="F55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H55" t="s">
         <v>7</v>
       </c>
       <c r="I55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J55" t="s">
-        <v>17</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0.2955</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>98</v>
+      </c>
+      <c r="B56" t="s">
         <v>99</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>100</v>
-      </c>
-      <c r="C56" t="s">
-        <v>101</v>
       </c>
       <c r="D56" t="n">
         <v>27.941201</v>
@@ -2624,33 +2456,30 @@
         <v>-82.82485</v>
       </c>
       <c r="F56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H56" t="s">
         <v>7</v>
       </c>
       <c r="I56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J56" t="s">
-        <v>17</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0.0067</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>101</v>
+      </c>
+      <c r="B57" t="s">
         <v>102</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>103</v>
-      </c>
-      <c r="C57" t="s">
-        <v>104</v>
       </c>
       <c r="D57" t="n">
         <v>27.822104</v>
@@ -2659,33 +2488,30 @@
         <v>-82.811026</v>
       </c>
       <c r="F57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H57" t="s">
         <v>7</v>
       </c>
       <c r="I57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J57" t="s">
-        <v>17</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0.0075</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
+        <v>104</v>
+      </c>
+      <c r="B58" t="s">
         <v>105</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>106</v>
-      </c>
-      <c r="C58" t="s">
-        <v>107</v>
       </c>
       <c r="D58" t="n">
         <v>27.789688</v>
@@ -2694,33 +2520,30 @@
         <v>-82.761709</v>
       </c>
       <c r="F58" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H58" t="s">
         <v>7</v>
       </c>
       <c r="I58" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J58" t="s">
-        <v>17</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0.0541</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B59" t="s">
         <v>105</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>106</v>
-      </c>
-      <c r="C59" t="s">
-        <v>107</v>
       </c>
       <c r="D59" t="n">
         <v>27.789688</v>
@@ -2729,33 +2552,30 @@
         <v>-82.761709</v>
       </c>
       <c r="F59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H59" t="s">
         <v>7</v>
       </c>
       <c r="I59" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J59" t="s">
-        <v>17</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0.0588</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
+        <v>104</v>
+      </c>
+      <c r="B60" t="s">
         <v>105</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>106</v>
-      </c>
-      <c r="C60" t="s">
-        <v>107</v>
       </c>
       <c r="D60" t="n">
         <v>27.789688</v>
@@ -2764,33 +2584,30 @@
         <v>-82.761709</v>
       </c>
       <c r="F60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H60" t="s">
         <v>7</v>
       </c>
       <c r="I60" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J60" t="s">
-        <v>17</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0.0108</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>107</v>
+      </c>
+      <c r="B61" t="s">
         <v>108</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>109</v>
-      </c>
-      <c r="C61" t="s">
-        <v>110</v>
       </c>
       <c r="D61" t="n">
         <v>27.727523</v>
@@ -2799,33 +2616,30 @@
         <v>-82.713078</v>
       </c>
       <c r="F61" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H61" t="s">
         <v>7</v>
       </c>
       <c r="I61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J61" t="s">
-        <v>17</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0.1197</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>107</v>
+      </c>
+      <c r="B62" t="s">
         <v>108</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>109</v>
-      </c>
-      <c r="C62" t="s">
-        <v>110</v>
       </c>
       <c r="D62" t="n">
         <v>27.727523</v>
@@ -2834,33 +2648,30 @@
         <v>-82.713078</v>
       </c>
       <c r="F62" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H62" t="s">
         <v>7</v>
       </c>
       <c r="I62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J62" t="s">
-        <v>17</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0.3092</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>107</v>
+      </c>
+      <c r="B63" t="s">
         <v>108</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>109</v>
-      </c>
-      <c r="C63" t="s">
-        <v>110</v>
       </c>
       <c r="D63" t="n">
         <v>27.727523</v>
@@ -2869,33 +2680,30 @@
         <v>-82.713078</v>
       </c>
       <c r="F63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H63" t="s">
         <v>7</v>
       </c>
       <c r="I63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J63" t="s">
-        <v>17</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0.0143</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>110</v>
+      </c>
+      <c r="B64" t="s">
         <v>111</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>112</v>
-      </c>
-      <c r="C64" t="s">
-        <v>113</v>
       </c>
       <c r="D64" t="n">
         <v>27.663779</v>
@@ -2904,33 +2712,30 @@
         <v>-82.704781</v>
       </c>
       <c r="F64" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H64" t="s">
         <v>7</v>
       </c>
       <c r="I64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J64" t="s">
-        <v>17</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0.019</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>110</v>
+      </c>
+      <c r="B65" t="s">
         <v>111</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>112</v>
-      </c>
-      <c r="C65" t="s">
-        <v>113</v>
       </c>
       <c r="D65" t="n">
         <v>27.663779</v>
@@ -2939,22 +2744,19 @@
         <v>-82.704781</v>
       </c>
       <c r="F65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H65" t="s">
         <v>7</v>
       </c>
       <c r="I65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J65" t="s">
-        <v>17</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0.0097</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -3188,22 +2990,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="ebcefb84-3943-4c67-86e4-95e0d5522177" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="20a86c8e-58bd-487e-986c-19c6170a5cfd">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ebcefb84-3943-4c67-86e4-95e0d5522177" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA860E7B-C6C1-41B2-B5A7-3464278F5A43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{059C1DF1-9578-4CCA-9776-5E1449DA3198}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C74B140-7ECF-43D3-AD87-F5B073C06D17}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB18382F-2912-4E55-9E40-2E332881F1E5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F875CDB8-75E0-418A-B318-969C4ADAA6F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0BC021A-39CD-48DB-BB0C-0DA8E55D25B9}"/>
 </file>